--- a/docs/reference-forms/output/xlsx/TAI-FORM-MNT-03.xlsx
+++ b/docs/reference-forms/output/xlsx/TAI-FORM-MNT-03.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설비보전 작업일지" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'설비보전 작업일지'!$A$1:$D$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'설비보전 작업일지'!$A$1:$D$224</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -575,86 +575,39 @@
     <row r="20" ht="14" customHeight="1"/>
     <row r="21" ht="14" customHeight="1"/>
     <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>작업 범위 및 내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="14" customHeight="1"/>
-    <row r="25" ht="14" customHeight="1"/>
-    <row r="26" ht="14" customHeight="1"/>
-    <row r="27" ht="14" customHeight="1"/>
-    <row r="28" ht="14" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>작업 결과</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="14" customHeight="1">
-      <c r="A29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30" ht="14" customHeight="1"/>
-    <row r="31" ht="14" customHeight="1"/>
-    <row r="32" ht="14" customHeight="1"/>
-    <row r="33" ht="14" customHeight="1"/>
-    <row r="34" ht="14" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>잔여 위험 및 특이사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="14" customHeight="1">
-      <c r="A35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36" ht="14" customHeight="1"/>
-    <row r="37" ht="14" customHeight="1"/>
-    <row r="38" ht="14" customHeight="1"/>
-    <row r="39" ht="14" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>작업자</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>감독자</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="6" t="inlineStr"/>
-      <c r="C40" s="6" t="inlineStr"/>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="6" t="inlineStr"/>
+      <c r="C23" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="16">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D10"/>
     <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D21"/>
     <mergeCell ref="A12:D16"/>
     <mergeCell ref="D3"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A23:D27"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A29:D33"/>
-    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="B2"/>
+    <mergeCell ref="D2"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B3"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A18:D21"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B2"/>
-    <mergeCell ref="D2"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A6:D10"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A35:D38"/>
-    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>

--- a/docs/reference-forms/output/xlsx/TAI-FORM-MNT-03.xlsx
+++ b/docs/reference-forms/output/xlsx/TAI-FORM-MNT-03.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설비보전 작업일지" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'설비보전 작업일지'!$A$1:$D$224</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'설비보전 작업일지'!$A$1:$D$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
